--- a/report/datasets/dev_v1_original_vs_dev_v1_dictionary_gpt_comparison.xlsx
+++ b/report/datasets/dev_v1_original_vs_dev_v1_dictionary_gpt_comparison.xlsx
@@ -2,15 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dev_v1_orig vs dev_v1_dict" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dev_v1_gpt vs dev_v1_dict" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dev_v1 orig vs gpt vs dict" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,10 +28,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -38,30 +42,57 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-        <bgColor rgb="00BDD7EE"/>
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -71,33 +102,168 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color rgb="00000000"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
@@ -107,40 +273,215 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -504,262 +845,237 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="12.21875" bestFit="1" customWidth="1" style="71" min="1" max="1"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" style="71" min="2" max="2"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="3" max="3"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="4" max="4"/>
+    <col width="18" customWidth="1" style="71" min="5" max="5"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="6" max="6"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="7" max="7"/>
+    <col width="16" bestFit="1" customWidth="1" style="71" min="8" max="8"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="9" max="9"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="10" max="10"/>
+    <col width="18" customWidth="1" style="71" min="11" max="11"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="12" max="12"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="13" max="13"/>
+    <col width="16" bestFit="1" customWidth="1" style="71" min="14" max="14"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="15" max="15"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="16" max="16"/>
+    <col width="16" bestFit="1" customWidth="1" style="71" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="78" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="80" t="inlineStr">
         <is>
           <t>BLEU</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="66" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>chrF</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="G1" s="66" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="62" t="inlineStr">
         <is>
           <t>Term Accuracy %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="66" t="n"/>
+      <c r="K1" s="67" t="n"/>
+      <c r="L1" s="62" t="inlineStr">
         <is>
           <t>Macro Consistency</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="M1" s="66" t="n"/>
+      <c r="N1" s="67" t="n"/>
+      <c r="O1" s="62" t="inlineStr">
         <is>
           <t>Weighted Consistency</t>
         </is>
       </c>
+      <c r="P1" s="66" t="n"/>
+      <c r="Q1" s="67" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="1" t="inlineStr">
+      <c r="B2" s="63" t="n"/>
+      <c r="C2" s="56" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="D2" s="64" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="E2" s="57" t="inlineStr">
         <is>
           <t>best</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="64" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="G2" s="64" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="H2" s="57" t="inlineStr">
         <is>
           <t>best</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="56" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="J2" s="64" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="K2" s="57" t="inlineStr">
         <is>
           <t>best</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="56" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="M2" s="64" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="N2" s="57" t="inlineStr">
         <is>
           <t>best</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" s="56" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="P2" s="64" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="Q2" s="57" t="inlineStr">
         <is>
           <t>best</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>no_term</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>42.20540855453915</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="5" t="n">
         <v>42.46240345706781</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>66.85204020887328</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>66.98900998361339</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="17" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="17" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+      <c r="Q3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="82" t="n"/>
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>enru</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="8" t="n">
         <v>28.32727356805207</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="1" t="n">
         <v>28.60929856487324</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>59.20101726413657</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="1" t="n">
         <v>58.77559990341402</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v/>
-      </c>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="1" t="n"/>
+      <c r="K4" s="18" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="1" t="n"/>
+      <c r="N4" s="18" t="n"/>
+      <c r="O4" s="1" t="n"/>
+      <c r="P4" s="1" t="n"/>
+      <c r="Q4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="A5" s="63" t="n"/>
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
@@ -767,186 +1083,168 @@
       <c r="C5" s="8" t="n">
         <v>48.33209418068491</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="1" t="n">
         <v>47.58873418335617</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="1" t="n">
         <v>69.4225599096719</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="1" t="n">
         <v>69.07499761670046</v>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="I5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v/>
-      </c>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="19" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>proper_term</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>48.60395346478844</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>54.12488479371674</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>73.95915905230463</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>78.36526438321229</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>60.47008547008546</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="5" t="n">
         <v>70.56000000000002</v>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="n">
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>0.8969399042747305</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="5" t="n">
         <v>0.9288117048923646</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="n">
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
         <v>0.8061041292639158</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="5" t="n">
         <v>0.8423390081421178</v>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="82" t="n"/>
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>enru</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="8" t="n">
         <v>35.78789434132558</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="1" t="n">
         <v>43.49889848461612</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>66.59295499021476</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="1" t="n">
         <v>72.45995024990887</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n">
         <v>70.27027027027027</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="1" t="n">
         <v>73.90393294648615</v>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="n">
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>0.8918519997082257</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.929763008632753</v>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n">
+      <c r="N7" s="12" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>0.704061895551257</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="P7" s="1" t="n">
         <v>0.774401473296503</v>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="Q7" s="12" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="A8" s="63" t="n"/>
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
@@ -954,247 +1252,247 @@
       <c r="C8" s="8" t="n">
         <v>54.04341128435075</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="1" t="n">
         <v>64.83165350095547</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>75.47238108272256</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="1" t="n">
         <v>82.25934468449383</v>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="n">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
         <v>89.01734104046243</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="10" t="n">
         <v>92.94871794871796</v>
       </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="n">
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="n">
         <v>0.9054832968358699</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="10" t="n">
         <v>0.9527865808420228</v>
       </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="n">
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="n">
         <v>0.8042635658914731</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="P8" s="10" t="n">
         <v>0.8671814671814662</v>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="14" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="58" t="inlineStr">
         <is>
           <t>random_term</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>44.04531604854031</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>44.13955173233968</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>69.8203089040301</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>70.29743105335217</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>81.09339407744875</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="5" t="n">
         <v>81.32118451025056</v>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n">
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>0.9477034853425045</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="5" t="n">
         <v>0.9471340092605</v>
       </c>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="O9" s="5" t="n">
         <v>0.8819776714513556</v>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="P9" s="5" t="n">
         <v>0.8819776714513556</v>
       </c>
-      <c r="Q9" s="11" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t>tie</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="82" t="n"/>
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>enru</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="8" t="n">
         <v>31.58927049390612</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="1" t="n">
         <v>31.11982503412899</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="1" t="n">
         <v>62.85197160913458</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="1" t="n">
         <v>62.56348803612553</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="8" t="n">
         <v>81.31494804156677</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" s="1" t="n">
         <v>82.83373301358911</v>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="n">
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>0.9302609860163819</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.9302609860163819</v>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>tie</t>
         </is>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" s="1" t="n">
         <v>0.8558718861209968</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="P10" s="1" t="n">
         <v>0.855871886120997</v>
       </c>
-      <c r="Q10" s="11" t="inlineStr">
+      <c r="Q10" s="16" t="inlineStr">
         <is>
           <t>tie</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="A11" s="63" t="n"/>
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>51.42407802430437</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="10" t="n">
         <v>51.7801902333191</v>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n">
         <v>72.54511599310121</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="10" t="n">
         <v>72.88087064822034</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="n">
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n">
         <v>96.83544303797468</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="J11" s="10" t="n">
         <v>97.0886075949367</v>
       </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>dev_v1_dictionary</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="n">
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="n">
         <v>0.9597385244853599</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="10" t="n">
         <v>0.9592321953714358</v>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="O11" s="8" t="n">
+      <c r="O11" s="10" t="n">
         <v>0.9127272727272731</v>
       </c>
-      <c r="P11" s="8" t="n">
+      <c r="P11" s="10" t="n">
         <v>0.9109090909090913</v>
       </c>
-      <c r="Q11" s="9" t="inlineStr">
+      <c r="Q11" s="11" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1202,12 +1500,12 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="L1:N1"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A3:A5"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A3:A5"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A9:A11"/>
@@ -1215,4 +1513,837 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="71" min="1" max="1"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" style="71" min="2" max="2"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="3" max="3"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="4" max="4"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="5" max="5"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="6" max="6"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="7" max="7"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="8" max="8"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="9" max="9"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="10" max="10"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="11" max="11"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="B1" s="81" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C1" s="56" t="inlineStr">
+        <is>
+          <t>BLEU</t>
+        </is>
+      </c>
+      <c r="D1" s="83" t="n"/>
+      <c r="E1" s="81" t="inlineStr">
+        <is>
+          <t>chrF</t>
+        </is>
+      </c>
+      <c r="F1" s="84" t="n"/>
+      <c r="G1" s="56" t="inlineStr">
+        <is>
+          <t>Term Accuracy %</t>
+        </is>
+      </c>
+      <c r="H1" s="83" t="n"/>
+      <c r="I1" s="81" t="inlineStr">
+        <is>
+          <t>Macro Consistency</t>
+        </is>
+      </c>
+      <c r="J1" s="84" t="n"/>
+      <c r="K1" s="81" t="inlineStr">
+        <is>
+          <t>Weighted Consistency</t>
+        </is>
+      </c>
+      <c r="L1" s="84" t="n"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="63" t="n"/>
+      <c r="C2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="D2" s="64" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="E2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="F2" s="57" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="G2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="H2" s="64" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="J2" s="57" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="K2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="L2" s="57" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="58" t="inlineStr">
+        <is>
+          <t>proper_term</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>ende</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="n">
+        <v>48.60395346478844</v>
+      </c>
+      <c r="D3" s="32" t="n">
+        <v>54.12488479371674</v>
+      </c>
+      <c r="E3" s="35" t="n">
+        <v>73.95915905230463</v>
+      </c>
+      <c r="F3" s="38" t="n">
+        <v>78.36526438321229</v>
+      </c>
+      <c r="G3" s="35" t="n">
+        <v>60.47008547008546</v>
+      </c>
+      <c r="H3" s="32" t="n">
+        <v>70.56000000000002</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <v>0.8969399042747305</v>
+      </c>
+      <c r="J3" s="38" t="n">
+        <v>0.9288117048923646</v>
+      </c>
+      <c r="K3" s="35" t="n">
+        <v>0.8061041292639158</v>
+      </c>
+      <c r="L3" s="38" t="n">
+        <v>0.8423390081421178</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="82" t="n"/>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>enru</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="n">
+        <v>35.78789434132558</v>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>43.49889848461612</v>
+      </c>
+      <c r="E4" s="36" t="n">
+        <v>66.59295499021476</v>
+      </c>
+      <c r="F4" s="39" t="n">
+        <v>72.45995024990887</v>
+      </c>
+      <c r="G4" s="36" t="n">
+        <v>70.27027027027027</v>
+      </c>
+      <c r="H4" s="33" t="n">
+        <v>73.90393294648615</v>
+      </c>
+      <c r="I4" s="36" t="n">
+        <v>0.8918519997082257</v>
+      </c>
+      <c r="J4" s="39" t="n">
+        <v>0.929763008632753</v>
+      </c>
+      <c r="K4" s="36" t="n">
+        <v>0.704061895551257</v>
+      </c>
+      <c r="L4" s="39" t="n">
+        <v>0.774401473296503</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="63" t="n"/>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="n">
+        <v>54.04341128435075</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>64.83165350095547</v>
+      </c>
+      <c r="E5" s="37" t="n">
+        <v>75.47238108272256</v>
+      </c>
+      <c r="F5" s="40" t="n">
+        <v>82.25934468449383</v>
+      </c>
+      <c r="G5" s="37" t="n">
+        <v>89.01734104046243</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>92.94871794871796</v>
+      </c>
+      <c r="I5" s="37" t="n">
+        <v>0.9054832968358699</v>
+      </c>
+      <c r="J5" s="40" t="n">
+        <v>0.9527865808420228</v>
+      </c>
+      <c r="K5" s="37" t="n">
+        <v>0.8042635658914731</v>
+      </c>
+      <c r="L5" s="40" t="n">
+        <v>0.8671814671814662</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="16.109375" bestFit="1" customWidth="1" style="71" min="1" max="1"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="3" max="3"/>
+    <col width="16.6640625" customWidth="1" style="71" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="5" max="5"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="6" max="6"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="7" max="7"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="8" max="8"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="9" max="9"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="10" max="10"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="11" max="11"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>dev_v1</t>
+        </is>
+      </c>
+      <c r="B1" s="81" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C1" s="81" t="inlineStr">
+        <is>
+          <t>BLEU</t>
+        </is>
+      </c>
+      <c r="D1" s="84" t="n"/>
+      <c r="E1" s="81" t="inlineStr">
+        <is>
+          <t>chrF</t>
+        </is>
+      </c>
+      <c r="F1" s="84" t="n"/>
+      <c r="G1" s="81" t="inlineStr">
+        <is>
+          <t>Term Accuracy %</t>
+        </is>
+      </c>
+      <c r="H1" s="84" t="n"/>
+      <c r="I1" s="81" t="inlineStr">
+        <is>
+          <t>Macro Consistency</t>
+        </is>
+      </c>
+      <c r="J1" s="84" t="n"/>
+      <c r="K1" s="81" t="inlineStr">
+        <is>
+          <t>Weighted Consistency</t>
+        </is>
+      </c>
+      <c r="L1" s="84" t="n"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="63" t="n"/>
+      <c r="C2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="D2" s="57" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="E2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="F2" s="57" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="G2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="H2" s="57" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I2" s="56" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="J2" s="57" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="K2" s="64" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="L2" s="57" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="58" t="inlineStr">
+        <is>
+          <t>proper_term</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>ende</t>
+        </is>
+      </c>
+      <c r="C3" s="50" t="n">
+        <v>53.1453355808675</v>
+      </c>
+      <c r="D3" s="41" t="n">
+        <v>54.12488479371674</v>
+      </c>
+      <c r="E3" s="50" t="n">
+        <v>77.62256268271634</v>
+      </c>
+      <c r="F3" s="41" t="n">
+        <v>78.36526438321229</v>
+      </c>
+      <c r="G3" s="45" t="n">
+        <v>74.98295841854123</v>
+      </c>
+      <c r="H3" s="55" t="n">
+        <v>70.56000000000002</v>
+      </c>
+      <c r="I3" s="45" t="n">
+        <v>0.9444055155334643</v>
+      </c>
+      <c r="J3" s="55" t="n">
+        <v>0.9288117048923646</v>
+      </c>
+      <c r="K3" s="47" t="n">
+        <v>0.9444055155334643</v>
+      </c>
+      <c r="L3" s="55" t="n">
+        <v>0.8423390081421178</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="82" t="n"/>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>enru</t>
+        </is>
+      </c>
+      <c r="C4" s="51" t="n">
+        <v>43.14643446007593</v>
+      </c>
+      <c r="D4" s="42" t="n">
+        <v>43.49889848461612</v>
+      </c>
+      <c r="E4" s="51" t="n">
+        <v>72.49607633493659</v>
+      </c>
+      <c r="F4" s="54" t="n">
+        <v>72.45995024990887</v>
+      </c>
+      <c r="G4" s="46" t="n">
+        <v>79.41860465116279</v>
+      </c>
+      <c r="H4" s="54" t="n">
+        <v>73.90393294648615</v>
+      </c>
+      <c r="I4" s="46" t="n">
+        <v>0.9410865653968022</v>
+      </c>
+      <c r="J4" s="54" t="n">
+        <v>0.929763008632753</v>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>0.9410865653968022</v>
+      </c>
+      <c r="L4" s="54" t="n">
+        <v>0.774401473296503</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="63" t="n"/>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="n">
+        <v>65.50039397469644</v>
+      </c>
+      <c r="D5" s="52" t="n">
+        <v>64.83165350095547</v>
+      </c>
+      <c r="E5" s="53" t="n">
+        <v>82.2376779517852</v>
+      </c>
+      <c r="F5" s="44" t="n">
+        <v>82.25934468449383</v>
+      </c>
+      <c r="G5" s="43" t="n">
+        <v>93.16479400749064</v>
+      </c>
+      <c r="H5" s="52" t="n">
+        <v>92.94871794871796</v>
+      </c>
+      <c r="I5" s="43" t="n">
+        <v>0.9592626054286718</v>
+      </c>
+      <c r="J5" s="52" t="n">
+        <v>0.9527865808420228</v>
+      </c>
+      <c r="K5" s="49" t="n">
+        <v>0.9592626054286718</v>
+      </c>
+      <c r="L5" s="52" t="n">
+        <v>0.8671814671814662</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dictionary_expand</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="71" min="1" max="1"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="3" max="3"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="4" max="4"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="5" max="5"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="6" max="6"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="7" max="7"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="8" max="8"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="9" max="9"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="10" max="10"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="11" max="11"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="12" max="12"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="13" max="13"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="14" max="14"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" style="71" min="15" max="15"/>
+    <col width="12" bestFit="1" customWidth="1" style="71" min="16" max="16"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="71" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>dev_v1</t>
+        </is>
+      </c>
+      <c r="B1" s="81" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C1" s="85" t="inlineStr">
+        <is>
+          <t>BLEU</t>
+        </is>
+      </c>
+      <c r="E1" s="72" t="n"/>
+      <c r="F1" s="85" t="inlineStr">
+        <is>
+          <t>chrF</t>
+        </is>
+      </c>
+      <c r="H1" s="72" t="n"/>
+      <c r="I1" s="85" t="inlineStr">
+        <is>
+          <t>Term Accuracy %</t>
+        </is>
+      </c>
+      <c r="K1" s="72" t="n"/>
+      <c r="L1" s="85" t="inlineStr">
+        <is>
+          <t>Macro Consistency</t>
+        </is>
+      </c>
+      <c r="N1" s="72" t="n"/>
+      <c r="O1" s="85" t="inlineStr">
+        <is>
+          <t>Weighted Consistency</t>
+        </is>
+      </c>
+      <c r="Q1" s="72" t="n"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="63" t="n"/>
+      <c r="C2" s="68" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="D2" s="65" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="E2" s="80" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="F2" s="68" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="G2" s="65" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="H2" s="80" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="I2" s="68" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="J2" s="65" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="K2" s="80" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="L2" s="68" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="M2" s="65" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="N2" s="80" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+      <c r="O2" s="68" t="inlineStr">
+        <is>
+          <t>dev_v1_original</t>
+        </is>
+      </c>
+      <c r="P2" s="65" t="inlineStr">
+        <is>
+          <t>dev_v1_gpt</t>
+        </is>
+      </c>
+      <c r="Q2" s="80" t="inlineStr">
+        <is>
+          <t>dev_v1_dictionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="58" t="inlineStr">
+        <is>
+          <t>proper_term</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ende</t>
+        </is>
+      </c>
+      <c r="C3" s="86" t="n">
+        <v>48.60395346478844</v>
+      </c>
+      <c r="D3" s="87" t="n">
+        <v>53.1453355808675</v>
+      </c>
+      <c r="E3" s="88" t="n">
+        <v>54.12488479371674</v>
+      </c>
+      <c r="F3" s="86" t="n">
+        <v>73.95915905230463</v>
+      </c>
+      <c r="G3" s="87" t="n">
+        <v>77.62256268271634</v>
+      </c>
+      <c r="H3" s="88" t="n">
+        <v>78.36526438321229</v>
+      </c>
+      <c r="I3" s="86" t="n">
+        <v>60.47008547008546</v>
+      </c>
+      <c r="J3" s="89" t="n">
+        <v>74.98295841854123</v>
+      </c>
+      <c r="K3" s="90" t="n">
+        <v>70.56000000000002</v>
+      </c>
+      <c r="L3" s="86" t="n">
+        <v>0.8969399042747305</v>
+      </c>
+      <c r="M3" s="89" t="n">
+        <v>0.9444055155334643</v>
+      </c>
+      <c r="N3" s="90" t="n">
+        <v>0.9288117048923646</v>
+      </c>
+      <c r="O3" s="86" t="n">
+        <v>0.8061041292639158</v>
+      </c>
+      <c r="P3" s="89" t="n">
+        <v>0.9444055155334643</v>
+      </c>
+      <c r="Q3" s="90" t="n">
+        <v>0.8423390081421178</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="82" t="n"/>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>enru</t>
+        </is>
+      </c>
+      <c r="C4" s="91" t="n">
+        <v>35.78789434132558</v>
+      </c>
+      <c r="D4" s="92" t="n">
+        <v>43.14643446007593</v>
+      </c>
+      <c r="E4" s="93" t="n">
+        <v>43.49889848461612</v>
+      </c>
+      <c r="F4" s="91" t="n">
+        <v>66.59295499021476</v>
+      </c>
+      <c r="G4" s="94" t="n">
+        <v>72.49607633493659</v>
+      </c>
+      <c r="H4" s="95" t="n">
+        <v>72.45995024990887</v>
+      </c>
+      <c r="I4" s="91" t="n">
+        <v>70.27027027027027</v>
+      </c>
+      <c r="J4" s="94" t="n">
+        <v>79.41860465116279</v>
+      </c>
+      <c r="K4" s="95" t="n">
+        <v>73.90393294648615</v>
+      </c>
+      <c r="L4" s="91" t="n">
+        <v>0.8918519997082257</v>
+      </c>
+      <c r="M4" s="94" t="n">
+        <v>0.9410865653968022</v>
+      </c>
+      <c r="N4" s="95" t="n">
+        <v>0.929763008632753</v>
+      </c>
+      <c r="O4" s="91" t="n">
+        <v>0.704061895551257</v>
+      </c>
+      <c r="P4" s="94" t="n">
+        <v>0.9410865653968022</v>
+      </c>
+      <c r="Q4" s="95" t="n">
+        <v>0.774401473296503</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="63" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C5" s="96" t="n">
+        <v>54.04341128435075</v>
+      </c>
+      <c r="D5" s="97" t="n">
+        <v>65.50039397469644</v>
+      </c>
+      <c r="E5" s="98" t="n">
+        <v>64.83165350095547</v>
+      </c>
+      <c r="F5" s="96" t="n">
+        <v>75.47238108272256</v>
+      </c>
+      <c r="G5" s="99" t="n">
+        <v>82.2376779517852</v>
+      </c>
+      <c r="H5" s="100" t="n">
+        <v>82.25934468449383</v>
+      </c>
+      <c r="I5" s="96" t="n">
+        <v>89.01734104046243</v>
+      </c>
+      <c r="J5" s="97" t="n">
+        <v>93.16479400749064</v>
+      </c>
+      <c r="K5" s="98" t="n">
+        <v>92.94871794871796</v>
+      </c>
+      <c r="L5" s="96" t="n">
+        <v>0.9054832968358699</v>
+      </c>
+      <c r="M5" s="97" t="n">
+        <v>0.9592626054286718</v>
+      </c>
+      <c r="N5" s="98" t="n">
+        <v>0.9527865808420228</v>
+      </c>
+      <c r="O5" s="96" t="n">
+        <v>0.8042635658914731</v>
+      </c>
+      <c r="P5" s="97" t="n">
+        <v>0.9592626054286718</v>
+      </c>
+      <c r="Q5" s="98" t="n">
+        <v>0.8671814671814662</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>